--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-11-2025.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>£10.68</t>
+          <t>£9.75</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>£11.98</t>
+          <t>£11.55</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -820,7 +820,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>£14.79</t>
+          <t>£14.05</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -941,7 +941,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>£15.64</t>
+          <t>£15.09</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>£19.20</t>
+          <t>£18.24</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>£22.04</t>
+          <t>£20.29</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>£21.09</t>
+          <t>£20.40</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>£25.25</t>
+          <t>£23.89</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>£27.29</t>
+          <t>£25.65</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>£26.48</t>
+          <t>£25.16</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>£34.62</t>
+          <t>£32.89</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>£32.31</t>
+          <t>£30.55</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>£40.22</t>
+          <t>£37.75</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>£40.25</t>
+          <t>£37.88</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>£39.63</t>
+          <t>£37.40</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bfe5e8e5+80021]
-	GetHandleVerifier [0x0x7ff7bfe5e940+80112]
-	(No symbol) [0x0x7ff7bfbe060f]
-	(No symbol) [0x0x7ff7bfc38854]
-	(No symbol) [0x0x7ff7bfc38b1c]
-	(No symbol) [0x0x7ff7bfc8c927]
-	(No symbol) [0x0x7ff7bfc6126f]
-	(No symbol) [0x0x7ff7bfc8968a]
-	(No symbol) [0x0x7ff7bfc61003]
-	(No symbol) [0x0x7ff7bfc295d1]
-	(No symbol) [0x0x7ff7bfc2a3f3]
-	GetHandleVerifier [0x0x7ff7c011dc7d+2960429]
-	GetHandleVerifier [0x0x7ff7c0117f3a+2936554]
-	GetHandleVerifier [0x0x7ff7c0138977+3070247]
-	GetHandleVerifier [0x0x7ff7bfe783ce+185214]
-	GetHandleVerifier [0x0x7ff7bfe7fe1f+216527]
-	GetHandleVerifier [0x0x7ff7bfe67b24+117460]
-	GetHandleVerifier [0x0x7ff7bfe67cdf+117903]
-	GetHandleVerifier [0x0x7ff7bfe4dbb8+11112]
+	GetHandleVerifier [0x0x7ff7dc82e8e5+80021]
+	GetHandleVerifier [0x0x7ff7dc82e940+80112]
+	(No symbol) [0x0x7ff7dc5b060f]
+	(No symbol) [0x0x7ff7dc608854]
+	(No symbol) [0x0x7ff7dc608b1c]
+	(No symbol) [0x0x7ff7dc65c927]
+	(No symbol) [0x0x7ff7dc63126f]
+	(No symbol) [0x0x7ff7dc65968a]
+	(No symbol) [0x0x7ff7dc631003]
+	(No symbol) [0x0x7ff7dc5f95d1]
+	(No symbol) [0x0x7ff7dc5fa3f3]
+	GetHandleVerifier [0x0x7ff7dcaedc7d+2960429]
+	GetHandleVerifier [0x0x7ff7dcae7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7dcb08977+3070247]
+	GetHandleVerifier [0x0x7ff7dc8483ce+185214]
+	GetHandleVerifier [0x0x7ff7dc84fe1f+216527]
+	GetHandleVerifier [0x0x7ff7dc837b24+117460]
+	GetHandleVerifier [0x0x7ff7dc837cdf+117903]
+	GetHandleVerifier [0x0x7ff7dc81dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
